--- a/Model Validations/Training Pairings.xlsx
+++ b/Model Validations/Training Pairings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important File\Crew Management\POC\Vendors\Mu Sigma\Model Output\Model Validations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important File\Crew Management\POC\Model Evaluation\Fixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D818AD18-3808-4F9C-8018-25B15D421F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24B1F9A-9843-455F-A0A1-BCE04569ADAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="35">
   <si>
-    <t>Instrutor</t>
-  </si>
-  <si>
     <t>Trainee</t>
   </si>
   <si>
@@ -141,6 +138,9 @@
   </si>
   <si>
     <t>ALUT</t>
+  </si>
+  <si>
+    <t>Instructor</t>
   </si>
 </sst>
 </file>
@@ -267,7 +267,7 @@
   <autoFilter ref="A1:D43" xr:uid="{4877481E-1A58-48BE-B48A-6F4615613E70}"/>
   <tableColumns count="4">
     <tableColumn id="5" xr3:uid="{407A9BB9-3800-4C04-89B8-E44AF4D8D6FD}" name="Date" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{078106E2-52AC-4063-A2C4-16153FC6CF9E}" name="Instrutor" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{078106E2-52AC-4063-A2C4-16153FC6CF9E}" name="Instructor" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{9B153B51-624A-4C2B-8609-D09188FE2CDE}" name="Trainee" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{27291A42-C873-4DF9-BBB9-E13D7C25F2ED}" name="Training Type" dataDxfId="0"/>
   </tableColumns>
@@ -549,16 +549,16 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -567,13 +567,13 @@
         <v>45901</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -582,13 +582,13 @@
         <v>45901</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -597,13 +597,13 @@
         <v>45901</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -612,13 +612,13 @@
         <v>45902</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -627,13 +627,13 @@
         <v>45902</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -642,28 +642,28 @@
         <v>45903</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
-        <f t="shared" ref="A8:A11" si="0">DATE(2025,9,3)</f>
+        <f t="shared" ref="A8:A10" si="0">DATE(2025,9,3)</f>
         <v>45903</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2"/>
     </row>
@@ -673,13 +673,13 @@
         <v>45903</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -688,13 +688,13 @@
         <v>45903</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -703,13 +703,13 @@
         <v>45904</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -718,13 +718,13 @@
         <v>45904</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -733,13 +733,13 @@
         <v>45904</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>45904</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -763,13 +763,13 @@
         <v>45904</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -778,13 +778,13 @@
         <v>45904</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -793,13 +793,13 @@
         <v>45905</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -808,13 +808,13 @@
         <v>45905</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -823,13 +823,13 @@
         <v>45905</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -838,13 +838,13 @@
         <v>45905</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -853,13 +853,13 @@
         <v>45905</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -868,28 +868,28 @@
         <v>45906</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <f t="shared" ref="A23:A29" si="3">DATE(2025,9,6)</f>
+        <f t="shared" ref="A23:A28" si="3">DATE(2025,9,6)</f>
         <v>45906</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -898,13 +898,13 @@
         <v>45906</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -913,13 +913,13 @@
         <v>45906</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -928,13 +928,13 @@
         <v>45906</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -943,13 +943,13 @@
         <v>45906</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -958,13 +958,13 @@
         <v>45906</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -973,13 +973,13 @@
         <v>45907</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -988,13 +988,13 @@
         <v>45907</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1003,13 +1003,13 @@
         <v>45907</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1018,13 +1018,13 @@
         <v>45907</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1033,13 +1033,13 @@
         <v>45908</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1048,13 +1048,13 @@
         <v>45908</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1063,13 +1063,13 @@
         <v>45908</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1078,13 +1078,13 @@
         <v>45908</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1093,13 +1093,13 @@
         <v>45909</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1108,13 +1108,13 @@
         <v>45909</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1123,13 +1123,13 @@
         <v>45909</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -1138,13 +1138,13 @@
         <v>45909</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1153,13 +1153,13 @@
         <v>45910</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1168,13 +1168,13 @@
         <v>45910</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1183,13 +1183,13 @@
         <v>45910</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
